--- a/data/trans_orig/P21D5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146332</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153474</t>
+          <t>153534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118556</t>
+          <t>118966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124504</t>
+          <t>124656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>268964</t>
+          <t>268370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277455</t>
+          <t>277393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174096</t>
+          <t>173384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>199518</t>
+          <t>198878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210764</t>
+          <t>210189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225853</t>
+          <t>226164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392355</t>
+          <t>391833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>422203</t>
+          <t>420999</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48690</t>
+          <t>50515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87608</t>
+          <t>87548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94254</t>
+          <t>94279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129666</t>
+          <t>129369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>138792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220462</t>
+          <t>220927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232422</t>
+          <t>232383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2935</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124266</t>
+          <t>123712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137076</t>
+          <t>137134</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>228037</t>
+          <t>228220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>242415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>358953</t>
+          <t>357988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>377839</t>
+          <t>377891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,62 +2811,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>61355</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>68894</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58262</t>
+          <t>58135</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>66790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122912</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134122</t>
+          <t>134180</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1857</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119565</t>
+          <t>119635</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125121</t>
+          <t>125123</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110600</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229357</t>
+          <t>229572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235256</t>
+          <t>235477</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3801,97 +3801,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>281637</t>
+          <t>283112</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>300727</t>
+          <t>300807</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>277173</t>
+          <t>278134</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>294778</t>
+          <t>294806</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>567257</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>591359</t>
+          <t>591145</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>39470</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4483,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>1338</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4337</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>103239</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>530388</t>
+          <t>530211</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>320605</t>
+          <t>321653</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>335055</t>
+          <t>335198</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>267245</t>
+          <t>293026</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>860032</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>449146</t>
+          <t>451720</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>631361</t>
+          <t>604599</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>816973</t>
+          <t>838681</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1581966</t>
+          <t>1584973</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1486961</t>
+          <t>1486267</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1519843</t>
+          <t>1519465</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2174383</t>
+          <t>2184149</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3085632</t>
+          <t>3086476</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>848528</t>
+          <t>817950</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>81291</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>134421</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1054898</t>
+          <t>1045858</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>151389</t>
+          <t>151719</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145688</t>
+          <t>146999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153534</t>
+          <t>153614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122618</t>
+          <t>134742</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118966</t>
+          <t>131244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124656</t>
+          <t>136856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>274007</t>
+          <t>286461</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>268370</t>
+          <t>281178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277393</t>
+          <t>289415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>189840</t>
+          <t>201137</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173384</t>
+          <t>185102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198878</t>
+          <t>210271</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>219839</t>
+          <t>234621</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210189</t>
+          <t>224845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226164</t>
+          <t>241034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>409679</t>
+          <t>435758</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>391833</t>
+          <t>419439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>420999</t>
+          <t>447896</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>595</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92281</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87548</t>
+          <t>85709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>92383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>135006</t>
+          <t>135723</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138792</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>227287</t>
+          <t>226210</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220927</t>
+          <t>219371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232383</t>
+          <t>231490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>576</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>576</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>132676</t>
+          <t>165610</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123712</t>
+          <t>156937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137134</t>
+          <t>170152</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>235921</t>
+          <t>190262</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>228220</t>
+          <t>184338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242415</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>368597</t>
+          <t>355871</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357988</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>377891</t>
+          <t>362609</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>82618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63545</t>
+          <t>70836</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>63659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66790</t>
+          <t>74381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>129803</t>
+          <t>150568</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>143116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134180</t>
+          <t>155811</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>872</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>123755</t>
+          <t>125046</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119635</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>112283</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106695</t>
+          <t>109391</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110607</t>
+          <t>113340</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>233309</t>
+          <t>237328</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229572</t>
+          <t>233833</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235477</t>
+          <t>239387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,22 +3753,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>371</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>371</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>293206</t>
+          <t>331025</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>283112</t>
+          <t>317936</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>300807</t>
+          <t>339289</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>288223</t>
+          <t>334952</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>278134</t>
+          <t>325259</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>294806</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>581429</t>
+          <t>665977</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>566443</t>
+          <t>651618</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>591145</t>
+          <t>676818</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23661</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>27058</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>44135</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>311572</t>
+          <t>351651</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>294277</t>
+          <t>343060</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>332101</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>530211</t>
+          <t>350053</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>329228</t>
+          <t>384671</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>321653</t>
+          <t>373943</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>335198</t>
+          <t>391535</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>623504</t>
+          <t>727731</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>293026</t>
+          <t>714281</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>859552</t>
+          <t>738425</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>256287</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>451720</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>271751</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>604599</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4934,67 +4934,67 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>11889</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>11299</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5082,22 +5082,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1343683</t>
+          <t>1487816</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>838681</t>
+          <t>1464914</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1584973</t>
+          <t>1505429</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1503933</t>
+          <t>1598089</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1486267</t>
+          <t>1580219</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1519465</t>
+          <t>1613685</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2847617</t>
+          <t>3085905</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2184149</t>
+          <t>3059035</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3086476</t>
+          <t>3108915</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>306874</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>817950</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>74456</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>54084</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>81291</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>374372</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1045858</t>
+          <t>167189</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,67 +5538,67 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>25322</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>16975</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>36487</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>24340</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>15669</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>37149</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5616,67 +5616,67 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
